--- a/Tests/tests.xlsx
+++ b/Tests/tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waite\Documents\GitHub\tbXLLerator\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964C5A80-A916-4AA7-85AA-7E1BAE868523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8D9494-E3E1-41CE-A44B-ED8CF58D31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="396" windowWidth="19764" windowHeight="13284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="396" windowWidth="19026" windowHeight="13284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="udf tests" sheetId="1" r:id="rId1"/>
@@ -260,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -277,7 +277,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -287,8 +288,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,7 +569,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="35.7890625" customWidth="1"/>
@@ -587,14 +586,14 @@
       <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="str">
@@ -888,7 +887,7 @@
       </c>
       <c r="B24" s="4" cm="1">
         <f t="array" aca="1" ref="B24" ca="1">_xll.TBXLL_Now()</f>
-        <v>46082.320003935187</v>
+        <v>46084.662003472222</v>
       </c>
       <c r="C24" s="12"/>
       <c r="H24" s="7"/>
@@ -901,7 +900,7 @@
       </c>
       <c r="B25" s="4">
         <f ca="1">NOW()</f>
-        <v>46082.320003935187</v>
+        <v>46084.662003472222</v>
       </c>
       <c r="C25" s="6"/>
       <c r="H25" s="7"/>
@@ -966,7 +965,7 @@
       </c>
       <c r="B30" s="3" cm="1">
         <f t="array" aca="1" ref="B30" ca="1">_xll.TBXLL_RecalcCounter()</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6"/>
       <c r="H30" s="7"/>
@@ -1248,11 +1247,11 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>=TBXLL_SpeedSafe(100)</v>
+        <v>=TBXLL_SpeedSafe(100,10,10)</v>
       </c>
       <c r="B50" s="3" cm="1">
-        <f t="array" ref="B50">_xll.TBXLL_SpeedSafe(100)</f>
-        <v>66671645.919710793</v>
+        <f t="array" ref="B50">_xll.TBXLL_SpeedSafe(100,10,10)</f>
+        <v>1000</v>
       </c>
       <c r="C50" s="6"/>
       <c r="H50" s="7"/>
@@ -1260,11 +1259,11 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>=TBXLL_SpeedUnsafe(100)</v>
+        <v>=TBXLL_SpeedUnsafe(100,10,10)</v>
       </c>
       <c r="B51" s="3" cm="1">
-        <f t="array" ref="B51">_xll.TBXLL_SpeedUnsafe(100)</f>
-        <v>66671645.919710793</v>
+        <f t="array" ref="B51">_xll.TBXLL_SpeedUnsafe(100,10,10)</f>
+        <v>1000</v>
       </c>
       <c r="C51" s="6"/>
       <c r="H51" s="7"/>
@@ -1272,23 +1271,23 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="3" t="str">
         <f t="shared" ref="A52" ca="1" si="5">_xlfn.FORMULATEXT(B52)</f>
-        <v>=TBXLL_Timestamp()</v>
-      </c>
-      <c r="B52" s="16" cm="1">
-        <f t="array" aca="1" ref="B52" ca="1">_xll.TBXLL_Timestamp()</f>
-        <v>329241.8629525</v>
+        <v>=TBXLL_SpeedSafeQ(100,10,10)</v>
+      </c>
+      <c r="B52" s="3" cm="1">
+        <f t="array" ref="B52">_xll.TBXLL_SpeedSafeQ(100,10,10)</f>
+        <v>1000</v>
       </c>
       <c r="C52" s="6"/>
       <c r="H52" s="7"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="3" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v>=TBXLL_NumberName(9)</v>
-      </c>
-      <c r="B53" s="3" t="str" cm="1">
-        <f t="array" ref="B53">_xll.TBXLL_NumberName(9)</f>
-        <v>Nine</v>
+        <f t="shared" ref="A53" ca="1" si="6">_xlfn.FORMULATEXT(B53)</f>
+        <v>=TBXLL_SpeedSafeB(100,10,10)</v>
+      </c>
+      <c r="B53" s="3" cm="1">
+        <f t="array" ref="B53">_xll.TBXLL_SpeedSafeB(100,10,10)</f>
+        <v>1000</v>
       </c>
       <c r="C53" s="6"/>
       <c r="H53" s="7"/>
@@ -1296,60 +1295,72 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>=TBXLL_RomanNumeral(9)</v>
+        <v>=TBXLL_NumberName(9)</v>
       </c>
       <c r="B54" s="3" t="str" cm="1">
-        <f t="array" ref="B54">_xll.TBXLL_RomanNumeral(9)</f>
-        <v>IX</v>
-      </c>
+        <f t="array" ref="B54">_xll.TBXLL_NumberName(9)</f>
+        <v>Nine</v>
+      </c>
+      <c r="C54" s="6"/>
       <c r="H54" s="7"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>=TBXLL_AddDays(NOW(),7)</v>
-      </c>
-      <c r="B55" s="14" cm="1">
-        <f t="array" aca="1" ref="B55" ca="1">_xll.TBXLL_AddDays(NOW(),7)</f>
-        <v>46089.320003935187</v>
-      </c>
-      <c r="C55" s="6"/>
+        <v>=TBXLL_RomanNumeral(9)</v>
+      </c>
+      <c r="B55" s="3" t="str" cm="1">
+        <f t="array" ref="B55">_xll.TBXLL_RomanNumeral(9)</f>
+        <v>IX</v>
+      </c>
       <c r="H55" s="7"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>=TBXLL_SumFP12(D46:E48)</v>
-      </c>
-      <c r="B56" cm="1">
-        <f t="array" ref="B56">_xll.TBXLL_SumFP12(D46:E48)</f>
-        <v>16</v>
+        <v>=TBXLL_AddDays(NOW(),7)</v>
+      </c>
+      <c r="B56" s="14" cm="1">
+        <f t="array" aca="1" ref="B56" ca="1">_xll.TBXLL_AddDays(NOW(),7)</f>
+        <v>46091.662003472222</v>
       </c>
       <c r="C56" s="6"/>
       <c r="H56" s="7"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="20" t="str">
+      <c r="A57" s="3" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v>=TBXLL_SumFP12(D46:E48)</v>
+      </c>
+      <c r="B57" cm="1">
+        <f t="array" ref="B57">_xll.TBXLL_SumFP12(D46:E48)</f>
+        <v>16</v>
+      </c>
+      <c r="C57" s="6"/>
+      <c r="H57" s="7"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="16" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>=TBXLL_FormatArray({1,2,3},"item")</v>
       </c>
-      <c r="B57" s="13" t="str" cm="1">
-        <f t="array" ref="B57:D57">_xll.TBXLL_FormatArray({1,2,3},"item")</f>
+      <c r="B58" s="13" t="str" cm="1">
+        <f t="array" ref="B58:D58">_xll.TBXLL_FormatArray({1,2,3},"item")</f>
         <v>item_1</v>
       </c>
-      <c r="C57" s="15" t="str">
+      <c r="C58" s="15" t="str">
         <v>item_2</v>
       </c>
-      <c r="D57" s="10" t="str">
+      <c r="D58" s="10" t="str">
         <v>item_3</v>
       </c>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="11"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="21"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="11"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Tests/tests.xlsx
+++ b/Tests/tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waite\Documents\GitHub\tbXLLerator\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8D9494-E3E1-41CE-A44B-ED8CF58D31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DCC9A8-F382-4114-A3ED-F8FC9313E831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="396" windowWidth="19026" windowHeight="13284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="396" windowWidth="19026" windowHeight="13284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="udf tests" sheetId="1" r:id="rId1"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="B24" s="4" cm="1">
         <f t="array" aca="1" ref="B24" ca="1">_xll.TBXLL_Now()</f>
-        <v>46084.662003472222</v>
+        <v>46085.272216087964</v>
       </c>
       <c r="C24" s="12"/>
       <c r="H24" s="7"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="B25" s="4">
         <f ca="1">NOW()</f>
-        <v>46084.662003472222</v>
+        <v>46085.272216087964</v>
       </c>
       <c r="C25" s="6"/>
       <c r="H25" s="7"/>
@@ -965,7 +965,7 @@
       </c>
       <c r="B30" s="3" cm="1">
         <f t="array" aca="1" ref="B30" ca="1">_xll.TBXLL_RecalcCounter()</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" s="6"/>
       <c r="H30" s="7"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B56" s="14" cm="1">
         <f t="array" aca="1" ref="B56" ca="1">_xll.TBXLL_AddDays(NOW(),7)</f>
-        <v>46091.662003472222</v>
+        <v>46092.272216087964</v>
       </c>
       <c r="C56" s="6"/>
       <c r="H56" s="7"/>

--- a/Tests/tests.xlsx
+++ b/Tests/tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waite\Documents\GitHub\tbXLLerator\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A580CC-6394-4092-AAEA-64544C87E846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBC6DD5-F5CF-4120-84E4-3EB82428056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1098" yWindow="396" windowWidth="19026" windowHeight="13284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="udf tests" sheetId="1" r:id="rId1"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B24" s="3" cm="1">
         <f t="array" aca="1" ref="B24" ca="1">_xll.TBXLL_Now()</f>
-        <v>46086.466672453702</v>
+        <v>46087.387963541667</v>
       </c>
       <c r="C24" s="9"/>
       <c r="F24" s="3">
         <f ca="1">NOW()</f>
-        <v>46086.466672453702</v>
+        <v>46087.387963541667</v>
       </c>
       <c r="G24" s="2" t="b">
         <f ca="1">IF(ABS(B24-F24)&lt;0.01,TRUE, FALSE)</f>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B29" s="2" cm="1">
         <f t="array" aca="1" ref="B29" ca="1">_xll.TBXLL_RecalcCounter()</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="5"/>
       <c r="F29" s="2"/>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="B55" s="11" cm="1">
         <f t="array" aca="1" ref="B55" ca="1">_xll.TBXLL_AddDays(NOW(),7)</f>
-        <v>46093.466672453702</v>
+        <v>46094.387963541667</v>
       </c>
       <c r="C55" s="5"/>
       <c r="F55" s="14">
         <f ca="1">NOW()+7</f>
-        <v>46093.466672453702</v>
+        <v>46094.387963541667</v>
       </c>
       <c r="G55" s="2" t="b">
         <f t="shared" ca="1" si="5"/>
